--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-30).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-30).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>21</t>
+    <t>20</t>
   </si>
   <si>
-    <t>R$ 8.920,77</t>
+    <t>R$ 8.934,66</t>
   </si>
   <si>
-    <t>97.5</t>
+    <t>97.7</t>
   </si>
   <si>
     <t>64.3</t>
   </si>
   <si>
-    <t>6.70</t>
+    <t>6.69</t>
   </si>
   <si>
     <t>21.5</t>
@@ -959,7 +959,7 @@
     <t>6.4</t>
   </si>
   <si>
-    <t>32.4%</t>
+    <t>32.7%</t>
   </si>
   <si>
     <t>16.1%</t>
@@ -10127,7 +10127,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10157,18 +10157,30 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>11573.209999999999</v>
+      </c>
+      <c r="N58" s="6">
+        <v>132</v>
+      </c>
       <c r="O58" s="6">
         <v>102</v>
       </c>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>4.4328162790697672</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>17.740196078431371</v>
+      </c>
+      <c r="R58" s="8">
+        <v>6.2412544554455449</v>
+      </c>
       <c r="S58" s="8">
         <v>7</v>
       </c>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.37254901960784315</v>
+      </c>
       <c r="U58" s="9">
         <v>0.11764705882352941</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-30).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-30).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>20</t>
+    <t>17</t>
   </si>
   <si>
-    <t>R$ 8.934,66</t>
+    <t>R$ 8.881,03</t>
   </si>
   <si>
-    <t>97.7</t>
+    <t>97.0</t>
   </si>
   <si>
     <t>64.3</t>
   </si>
   <si>
-    <t>6.69</t>
+    <t>6.73</t>
   </si>
   <si>
-    <t>21.5</t>
+    <t>21.7</t>
   </si>
   <si>
-    <t>8.0</t>
+    <t>8.2</t>
   </si>
   <si>
     <t>6.4</t>
   </si>
   <si>
-    <t>32.7%</t>
+    <t>32.8%</t>
   </si>
   <si>
     <t>16.1%</t>
@@ -6801,7 +6801,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6831,14 +6831,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>5525.8699999999999</v>
+      </c>
+      <c r="N36" s="6">
+        <v>66</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>11.970454545454544</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>48.508630357142856</v>
+      </c>
+      <c r="R36" s="8">
+        <v>29.863332727272731</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.089285714285714288</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9090,7 +9102,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9120,14 +9132,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>685.29999999999995</v>
+      </c>
+      <c r="N51" s="6">
+        <v>7</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>5.9571428571428573</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>33.024999999999999</v>
+      </c>
+      <c r="R51" s="8">
+        <v>17.029174999999999</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14738,7 +14762,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14766,14 +14790,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>10187.92</v>
+      </c>
+      <c r="N89" s="6">
+        <v>88</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>8.5537875000000003</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>23.25</v>
+      </c>
+      <c r="R89" s="8">
+        <v>7.1205680851063828</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.0625</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
